--- a/data/ServiceMappingDundee.xlsx
+++ b/data/ServiceMappingDundee.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admf9\Documents\Code division\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S\Documents\GitHub\dundee-recovery-map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D96D047A-5FF3-472B-9969-DC5A62AAC161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC282D2-8F23-4C3B-92D5-AADDB8AE7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{63989B5C-3AE5-408C-9700-15EB407F54FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{63989B5C-3AE5-408C-9700-15EB407F54FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7247" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7247" uniqueCount="1091">
   <si>
     <t>Support Type</t>
   </si>
@@ -3161,9 +3161,6 @@
     <t>We deliver intensive nees-led personal development in communities and the Scottish wilderness, supporting our participants to gain life skills, stability and confidence to succeed for the rest of their lives.</t>
   </si>
   <si>
-    <t>Police Scotland 101</t>
-  </si>
-  <si>
     <t>City Wide</t>
   </si>
   <si>
@@ -3173,24 +3170,6 @@
     <t>We are committed to improving the lives of all in our communities. Working with our partners to encourage people onto the recovery path for addictions. City wide.</t>
   </si>
   <si>
-    <t>Police Scotland 102</t>
-  </si>
-  <si>
-    <t>Police Scotland 103</t>
-  </si>
-  <si>
-    <t>Police Scotland 104</t>
-  </si>
-  <si>
-    <t>Police Scotland 105</t>
-  </si>
-  <si>
-    <t>Police Scotland 106</t>
-  </si>
-  <si>
-    <t>Police Scotland 107</t>
-  </si>
-  <si>
     <t>01382 435808</t>
   </si>
   <si>
@@ -3594,6 +3573,9 @@
   </si>
   <si>
     <t>A self-help support of networks for families and friends of people with a current, suspected or former drug problem.</t>
+  </si>
+  <si>
+    <t>Police Scotland</t>
   </si>
 </sst>
 </file>
@@ -3750,7 +3732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3779,7 +3761,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4116,28 +4097,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664C24A9-C19D-4DF8-B051-D8F44559D396}">
   <dimension ref="A1:V395"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.77734375" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="86.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="86.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="74.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="91.33203125" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="74.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="91.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -13060,7 +13041,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="140" spans="1:22" ht="28.8">
+    <row r="140" spans="1:22" ht="30">
       <c r="A140" t="s">
         <v>72</v>
       </c>
@@ -23868,7 +23849,7 @@
         <v>923</v>
       </c>
       <c r="C311" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D311" t="s">
         <v>17</v>
@@ -23933,7 +23914,7 @@
         <v>923</v>
       </c>
       <c r="C312" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D312" t="s">
         <v>17</v>
@@ -23998,7 +23979,7 @@
         <v>923</v>
       </c>
       <c r="C313" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D313" t="s">
         <v>17</v>
@@ -24063,7 +24044,7 @@
         <v>923</v>
       </c>
       <c r="C314" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D314" t="s">
         <v>17</v>
@@ -24444,7 +24425,7 @@
         <v>72</v>
       </c>
       <c r="B320" t="s">
-        <v>952</v>
+        <v>1090</v>
       </c>
       <c r="D320" t="s">
         <v>123</v>
@@ -24468,13 +24449,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K320" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N320">
         <v>101</v>
       </c>
       <c r="P320" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q320" t="s">
         <v>26</v>
@@ -24486,7 +24467,7 @@
         <v>145</v>
       </c>
       <c r="U320" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="321" spans="1:22">
@@ -24494,7 +24475,7 @@
         <v>72</v>
       </c>
       <c r="B321" t="s">
-        <v>956</v>
+        <v>1090</v>
       </c>
       <c r="D321" t="s">
         <v>123</v>
@@ -24518,13 +24499,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K321" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N321">
         <v>101</v>
       </c>
       <c r="P321" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q321" t="s">
         <v>26</v>
@@ -24536,7 +24517,7 @@
         <v>145</v>
       </c>
       <c r="U321" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="322" spans="1:22">
@@ -24544,7 +24525,7 @@
         <v>72</v>
       </c>
       <c r="B322" t="s">
-        <v>957</v>
+        <v>1090</v>
       </c>
       <c r="D322" t="s">
         <v>123</v>
@@ -24568,13 +24549,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K322" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N322">
         <v>101</v>
       </c>
       <c r="P322" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q322" t="s">
         <v>26</v>
@@ -24586,7 +24567,7 @@
         <v>145</v>
       </c>
       <c r="U322" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="323" spans="1:22">
@@ -24594,7 +24575,7 @@
         <v>72</v>
       </c>
       <c r="B323" t="s">
-        <v>958</v>
+        <v>1090</v>
       </c>
       <c r="D323" t="s">
         <v>123</v>
@@ -24618,13 +24599,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K323" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N323">
         <v>101</v>
       </c>
       <c r="P323" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q323" t="s">
         <v>26</v>
@@ -24636,7 +24617,7 @@
         <v>145</v>
       </c>
       <c r="U323" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="324" spans="1:22">
@@ -24644,7 +24625,7 @@
         <v>72</v>
       </c>
       <c r="B324" t="s">
-        <v>959</v>
+        <v>1090</v>
       </c>
       <c r="D324" t="s">
         <v>123</v>
@@ -24668,13 +24649,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K324" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N324">
         <v>101</v>
       </c>
       <c r="P324" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q324" t="s">
         <v>26</v>
@@ -24686,7 +24667,7 @@
         <v>145</v>
       </c>
       <c r="U324" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="325" spans="1:22">
@@ -24694,7 +24675,7 @@
         <v>72</v>
       </c>
       <c r="B325" t="s">
-        <v>960</v>
+        <v>1090</v>
       </c>
       <c r="D325" t="s">
         <v>123</v>
@@ -24718,13 +24699,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K325" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N325">
         <v>101</v>
       </c>
       <c r="P325" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q325" t="s">
         <v>26</v>
@@ -24736,7 +24717,7 @@
         <v>145</v>
       </c>
       <c r="U325" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="326" spans="1:22">
@@ -24744,7 +24725,7 @@
         <v>72</v>
       </c>
       <c r="B326" t="s">
-        <v>961</v>
+        <v>1090</v>
       </c>
       <c r="D326" t="s">
         <v>123</v>
@@ -24768,13 +24749,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K326" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N326">
         <v>101</v>
       </c>
       <c r="P326" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q326" t="s">
         <v>26</v>
@@ -24786,7 +24767,7 @@
         <v>145</v>
       </c>
       <c r="U326" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="327" spans="1:22">
@@ -24794,10 +24775,10 @@
         <v>72</v>
       </c>
       <c r="B327" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="C327" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="D327" t="s">
         <v>78</v>
@@ -24830,13 +24811,13 @@
         <v>78</v>
       </c>
       <c r="N327" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="O327" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="P327" s="4" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="Q327" t="s">
         <v>78</v>
@@ -24845,10 +24826,10 @@
         <v>78</v>
       </c>
       <c r="U327" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="V327" s="4" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
     </row>
     <row r="328" spans="1:22">
@@ -24856,10 +24837,10 @@
         <v>72</v>
       </c>
       <c r="B328" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C328" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D328" t="s">
         <v>129</v>
@@ -24883,7 +24864,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K328" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L328" t="s">
         <v>245</v>
@@ -24892,13 +24873,13 @@
         <v>78</v>
       </c>
       <c r="N328" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="O328" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="P328" s="4" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="Q328" t="s">
         <v>26</v>
@@ -24910,7 +24891,7 @@
         <v>476</v>
       </c>
       <c r="U328" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="329" spans="1:22">
@@ -24918,10 +24899,10 @@
         <v>72</v>
       </c>
       <c r="B329" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C329" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D329" t="s">
         <v>129</v>
@@ -24945,7 +24926,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K329" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L329" t="s">
         <v>245</v>
@@ -24954,13 +24935,13 @@
         <v>78</v>
       </c>
       <c r="N329" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="O329" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="P329" s="4" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="Q329" t="s">
         <v>26</v>
@@ -24969,10 +24950,10 @@
         <v>78</v>
       </c>
       <c r="T329" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="U329" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="330" spans="1:22">
@@ -24980,10 +24961,10 @@
         <v>72</v>
       </c>
       <c r="B330" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C330" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D330" t="s">
         <v>129</v>
@@ -25007,7 +24988,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K330" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L330" t="s">
         <v>245</v>
@@ -25016,13 +24997,13 @@
         <v>78</v>
       </c>
       <c r="N330" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="O330" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="P330" s="4" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="Q330" t="s">
         <v>26</v>
@@ -25031,10 +25012,10 @@
         <v>78</v>
       </c>
       <c r="T330" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="U330" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="331" spans="1:22">
@@ -25042,10 +25023,10 @@
         <v>72</v>
       </c>
       <c r="B331" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C331" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D331" t="s">
         <v>129</v>
@@ -25069,7 +25050,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K331" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L331" t="s">
         <v>245</v>
@@ -25078,13 +25059,13 @@
         <v>78</v>
       </c>
       <c r="N331" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="O331" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="P331" s="4" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="Q331" t="s">
         <v>26</v>
@@ -25093,10 +25074,10 @@
         <v>78</v>
       </c>
       <c r="T331" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="U331" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="332" spans="1:22">
@@ -25104,10 +25085,10 @@
         <v>72</v>
       </c>
       <c r="B332" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C332" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D332" t="s">
         <v>129</v>
@@ -25131,7 +25112,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K332" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L332" t="s">
         <v>245</v>
@@ -25140,25 +25121,25 @@
         <v>78</v>
       </c>
       <c r="N332" t="s">
+        <v>965</v>
+      </c>
+      <c r="O332" t="s">
+        <v>966</v>
+      </c>
+      <c r="P332" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>26</v>
+      </c>
+      <c r="R332" t="s">
+        <v>78</v>
+      </c>
+      <c r="T332" t="s">
         <v>972</v>
       </c>
-      <c r="O332" t="s">
-        <v>973</v>
-      </c>
-      <c r="P332" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="Q332" t="s">
-        <v>26</v>
-      </c>
-      <c r="R332" t="s">
-        <v>78</v>
-      </c>
-      <c r="T332" t="s">
-        <v>979</v>
-      </c>
       <c r="U332" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="333" spans="1:22">
@@ -25166,10 +25147,10 @@
         <v>72</v>
       </c>
       <c r="B333" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="C333" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="D333" t="s">
         <v>123</v>
@@ -25193,19 +25174,19 @@
         <v>6.25E-2</v>
       </c>
       <c r="K333" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="L333" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="M333" t="s">
         <v>78</v>
       </c>
       <c r="N333" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="P333" s="4" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="Q333" t="s">
         <v>26</v>
@@ -25217,7 +25198,7 @@
         <v>145</v>
       </c>
       <c r="U333" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="334" spans="1:22">
@@ -25225,10 +25206,10 @@
         <v>72</v>
       </c>
       <c r="B334" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="C334" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="D334" t="s">
         <v>123</v>
@@ -25252,19 +25233,19 @@
         <v>6.25E-2</v>
       </c>
       <c r="K334" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="L334" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="M334" t="s">
         <v>78</v>
       </c>
       <c r="N334" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="P334" s="4" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="Q334" t="s">
         <v>26</v>
@@ -25276,7 +25257,7 @@
         <v>145</v>
       </c>
       <c r="U334" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="335" spans="1:22">
@@ -25284,7 +25265,7 @@
         <v>72</v>
       </c>
       <c r="B335" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="C335" t="s">
         <v>267</v>
@@ -25311,22 +25292,22 @@
         <v>78</v>
       </c>
       <c r="K335" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="L335" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="M335" t="s">
         <v>78</v>
       </c>
       <c r="N335" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="O335" s="4" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="P335" s="4" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="Q335" t="s">
         <v>26</v>
@@ -25335,10 +25316,10 @@
         <v>28</v>
       </c>
       <c r="T335" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="U335" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="336" spans="1:22">
@@ -25346,10 +25327,10 @@
         <v>72</v>
       </c>
       <c r="B336" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="C336" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="D336" t="s">
         <v>123</v>
@@ -25373,7 +25354,7 @@
         <v>78</v>
       </c>
       <c r="K336" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="L336" t="s">
         <v>745</v>
@@ -25382,13 +25363,13 @@
         <v>78</v>
       </c>
       <c r="N336" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="O336" s="4" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="P336" s="4" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="Q336" t="s">
         <v>26</v>
@@ -25397,10 +25378,10 @@
         <v>28</v>
       </c>
       <c r="T336" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="U336" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="337" spans="1:21">
@@ -25408,7 +25389,7 @@
         <v>72</v>
       </c>
       <c r="B337" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D337" t="s">
         <v>129</v>
@@ -25432,7 +25413,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K337" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="L337" t="s">
         <v>367</v>
@@ -25441,13 +25422,13 @@
         <v>78</v>
       </c>
       <c r="N337" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O337" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="P337" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="Q337" t="s">
         <v>26</v>
@@ -25456,10 +25437,10 @@
         <v>28</v>
       </c>
       <c r="T337" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="U337" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="338" spans="1:21">
@@ -25467,7 +25448,7 @@
         <v>72</v>
       </c>
       <c r="B338" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D338" t="s">
         <v>129</v>
@@ -25491,7 +25472,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K338" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="L338" t="s">
         <v>367</v>
@@ -25500,13 +25481,13 @@
         <v>78</v>
       </c>
       <c r="N338" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O338" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="P338" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="Q338" t="s">
         <v>26</v>
@@ -25515,10 +25496,10 @@
         <v>28</v>
       </c>
       <c r="T338" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="U338" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="339" spans="1:21">
@@ -25526,7 +25507,7 @@
         <v>72</v>
       </c>
       <c r="B339" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D339" t="s">
         <v>129</v>
@@ -25550,7 +25531,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K339" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="L339" t="s">
         <v>367</v>
@@ -25559,13 +25540,13 @@
         <v>78</v>
       </c>
       <c r="N339" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O339" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="P339" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="Q339" t="s">
         <v>26</v>
@@ -25574,10 +25555,10 @@
         <v>28</v>
       </c>
       <c r="T339" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="U339" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="340" spans="1:21">
@@ -25585,7 +25566,7 @@
         <v>72</v>
       </c>
       <c r="B340" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D340" t="s">
         <v>129</v>
@@ -25609,7 +25590,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K340" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="L340" t="s">
         <v>367</v>
@@ -25618,13 +25599,13 @@
         <v>78</v>
       </c>
       <c r="N340" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O340" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="P340" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="Q340" t="s">
         <v>26</v>
@@ -25633,10 +25614,10 @@
         <v>28</v>
       </c>
       <c r="T340" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="U340" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="341" spans="1:21">
@@ -25644,7 +25625,7 @@
         <v>72</v>
       </c>
       <c r="B341" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D341" t="s">
         <v>129</v>
@@ -25668,7 +25649,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K341" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="L341" t="s">
         <v>367</v>
@@ -25677,13 +25658,13 @@
         <v>78</v>
       </c>
       <c r="N341" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O341" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="P341" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="Q341" t="s">
         <v>26</v>
@@ -25692,10 +25673,10 @@
         <v>28</v>
       </c>
       <c r="T341" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="U341" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="342" spans="1:21">
@@ -25703,7 +25684,7 @@
         <v>72</v>
       </c>
       <c r="B342" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="C342" t="s">
         <v>267</v>
@@ -25730,22 +25711,22 @@
         <v>78</v>
       </c>
       <c r="K342" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L342" t="s">
         <v>245</v>
       </c>
       <c r="M342" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="N342" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="O342" s="4" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="P342" s="4" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="Q342" t="s">
         <v>78</v>
@@ -25754,18 +25735,18 @@
         <v>78</v>
       </c>
       <c r="U342" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="343" spans="1:21">
       <c r="A343" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B343" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C343" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="D343" t="s">
         <v>123</v>
@@ -25789,16 +25770,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K343" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N343" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O343" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P343" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q343" t="s">
         <v>26</v>
@@ -25807,18 +25788,18 @@
         <v>28</v>
       </c>
       <c r="U343" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="344" spans="1:21">
       <c r="A344" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B344" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C344" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D344" t="s">
         <v>123</v>
@@ -25842,16 +25823,16 @@
         <v>0.875</v>
       </c>
       <c r="K344" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N344" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O344" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P344" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q344" t="s">
         <v>26</v>
@@ -25860,18 +25841,18 @@
         <v>28</v>
       </c>
       <c r="U344" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="345" spans="1:21">
       <c r="A345" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B345" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C345" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D345" t="s">
         <v>123</v>
@@ -25895,16 +25876,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K345" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N345" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O345" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P345" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q345" t="s">
         <v>26</v>
@@ -25913,18 +25894,18 @@
         <v>28</v>
       </c>
       <c r="U345" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="346" spans="1:21">
       <c r="A346" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B346" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C346" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D346" t="s">
         <v>123</v>
@@ -25948,16 +25929,16 @@
         <v>0.875</v>
       </c>
       <c r="K346" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N346" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O346" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P346" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q346" t="s">
         <v>26</v>
@@ -25966,18 +25947,18 @@
         <v>28</v>
       </c>
       <c r="U346" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="347" spans="1:21">
       <c r="A347" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B347" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C347" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D347" t="s">
         <v>123</v>
@@ -26001,16 +25982,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K347" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N347" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O347" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P347" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q347" t="s">
         <v>26</v>
@@ -26019,18 +26000,18 @@
         <v>28</v>
       </c>
       <c r="U347" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="348" spans="1:21">
       <c r="A348" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B348" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C348" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D348" t="s">
         <v>123</v>
@@ -26054,16 +26035,16 @@
         <v>0.875</v>
       </c>
       <c r="K348" t="s">
-        <v>1091</v>
-      </c>
-      <c r="N348" s="24" t="s">
-        <v>1093</v>
+        <v>1084</v>
+      </c>
+      <c r="N348" t="s">
+        <v>1086</v>
       </c>
       <c r="O348" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P348" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q348" t="s">
         <v>26</v>
@@ -26072,18 +26053,18 @@
         <v>28</v>
       </c>
       <c r="U348" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="349" spans="1:21">
       <c r="A349" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B349" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C349" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D349" t="s">
         <v>123</v>
@@ -26107,16 +26088,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K349" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N349" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O349" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P349" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q349" t="s">
         <v>26</v>
@@ -26125,18 +26106,18 @@
         <v>28</v>
       </c>
       <c r="U349" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="350" spans="1:21">
       <c r="A350" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B350" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C350" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D350" t="s">
         <v>123</v>
@@ -26160,16 +26141,16 @@
         <v>0.875</v>
       </c>
       <c r="K350" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N350" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O350" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P350" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q350" t="s">
         <v>26</v>
@@ -26178,18 +26159,18 @@
         <v>28</v>
       </c>
       <c r="U350" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="351" spans="1:21">
       <c r="A351" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B351" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C351" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D351" t="s">
         <v>123</v>
@@ -26213,16 +26194,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K351" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N351" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O351" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P351" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q351" t="s">
         <v>26</v>
@@ -26231,18 +26212,18 @@
         <v>28</v>
       </c>
       <c r="U351" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="352" spans="1:21">
       <c r="A352" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B352" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C352" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="D352" t="s">
         <v>123</v>
@@ -26266,16 +26247,16 @@
         <v>0.875</v>
       </c>
       <c r="K352" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="N352" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="O352" s="4" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="P352" s="4" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="Q352" t="s">
         <v>26</v>
@@ -26284,7 +26265,7 @@
         <v>28</v>
       </c>
       <c r="U352" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="353" spans="1:22">
@@ -26292,10 +26273,10 @@
         <v>942</v>
       </c>
       <c r="B353" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="C353" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="D353" t="s">
         <v>123</v>
@@ -26319,19 +26300,19 @@
         <v>78</v>
       </c>
       <c r="K353" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="L353" t="s">
         <v>267</v>
       </c>
       <c r="N353" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="O353" s="4" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="P353" s="4" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="Q353" t="s">
         <v>26</v>
@@ -26340,10 +26321,10 @@
         <v>28</v>
       </c>
       <c r="T353" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="U353" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="354" spans="1:22">
@@ -26351,10 +26332,10 @@
         <v>72</v>
       </c>
       <c r="B354" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="C354" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="D354" t="s">
         <v>17</v>
@@ -26378,20 +26359,20 @@
         <v>78</v>
       </c>
       <c r="K354" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="L354" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="M354" t="s">
         <v>78</v>
       </c>
       <c r="N354" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="O354" s="4"/>
       <c r="P354" s="4" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="Q354" t="s">
         <v>26</v>
@@ -26400,10 +26381,10 @@
         <v>28</v>
       </c>
       <c r="T354" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="U354" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="355" spans="1:22">
@@ -26411,10 +26392,10 @@
         <v>72</v>
       </c>
       <c r="B355" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C355" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="D355" t="s">
         <v>123</v>
@@ -26438,7 +26419,7 @@
         <v>0.5</v>
       </c>
       <c r="K355" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L355" t="s">
         <v>635</v>
@@ -26453,16 +26434,16 @@
         <v>198</v>
       </c>
       <c r="S355" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="T355" t="s">
         <v>145</v>
       </c>
       <c r="U355" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V355" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="356" spans="1:22">
@@ -26470,10 +26451,10 @@
         <v>72</v>
       </c>
       <c r="B356" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C356" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="D356" t="s">
         <v>123</v>
@@ -26497,7 +26478,7 @@
         <v>0.5</v>
       </c>
       <c r="K356" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L356" t="s">
         <v>635</v>
@@ -26512,16 +26493,16 @@
         <v>198</v>
       </c>
       <c r="S356" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="T356" t="s">
         <v>145</v>
       </c>
       <c r="U356" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V356" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="357" spans="1:22">
@@ -26529,10 +26510,10 @@
         <v>72</v>
       </c>
       <c r="B357" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C357" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="D357" t="s">
         <v>123</v>
@@ -26556,7 +26537,7 @@
         <v>0.5</v>
       </c>
       <c r="K357" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L357" t="s">
         <v>635</v>
@@ -26571,16 +26552,16 @@
         <v>198</v>
       </c>
       <c r="S357" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="T357" t="s">
         <v>145</v>
       </c>
       <c r="U357" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V357" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="358" spans="1:22">
@@ -26588,10 +26569,10 @@
         <v>72</v>
       </c>
       <c r="B358" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C358" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D358" t="s">
         <v>123</v>
@@ -26615,7 +26596,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="K358" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L358" t="s">
         <v>635</v>
@@ -26633,10 +26614,10 @@
         <v>145</v>
       </c>
       <c r="U358" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V358" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="359" spans="1:22">
@@ -26644,10 +26625,10 @@
         <v>72</v>
       </c>
       <c r="B359" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C359" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D359" t="s">
         <v>123</v>
@@ -26671,7 +26652,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="K359" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L359" t="s">
         <v>635</v>
@@ -26689,10 +26670,10 @@
         <v>145</v>
       </c>
       <c r="U359" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V359" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="360" spans="1:22">
@@ -26700,10 +26681,10 @@
         <v>72</v>
       </c>
       <c r="B360" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C360" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D360" t="s">
         <v>123</v>
@@ -26727,7 +26708,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="K360" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L360" t="s">
         <v>635</v>
@@ -26745,10 +26726,10 @@
         <v>145</v>
       </c>
       <c r="U360" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V360" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="361" spans="1:22">
@@ -26756,10 +26737,10 @@
         <v>72</v>
       </c>
       <c r="B361" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C361" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D361" t="s">
         <v>123</v>
@@ -26783,7 +26764,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="K361" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L361" t="s">
         <v>635</v>
@@ -26801,10 +26782,10 @@
         <v>145</v>
       </c>
       <c r="U361" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V361" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="362" spans="1:22">
@@ -26812,10 +26793,10 @@
         <v>72</v>
       </c>
       <c r="B362" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C362" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D362" t="s">
         <v>123</v>
@@ -26839,7 +26820,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="K362" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L362" t="s">
         <v>635</v>
@@ -26857,10 +26838,10 @@
         <v>145</v>
       </c>
       <c r="U362" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V362" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="363" spans="1:22">
@@ -26868,10 +26849,10 @@
         <v>72</v>
       </c>
       <c r="B363" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C363" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="D363" t="s">
         <v>123</v>
@@ -26895,7 +26876,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="K363" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L363" t="s">
         <v>635</v>
@@ -26916,10 +26897,10 @@
         <v>145</v>
       </c>
       <c r="U363" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V363" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="364" spans="1:22">
@@ -26927,10 +26908,10 @@
         <v>72</v>
       </c>
       <c r="B364" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C364" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="D364" t="s">
         <v>123</v>
@@ -26954,7 +26935,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="K364" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L364" t="s">
         <v>635</v>
@@ -26975,10 +26956,10 @@
         <v>145</v>
       </c>
       <c r="U364" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V364" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="365" spans="1:22">
@@ -26986,10 +26967,10 @@
         <v>72</v>
       </c>
       <c r="B365" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C365" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="D365" t="s">
         <v>123</v>
@@ -27013,7 +26994,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="K365" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L365" t="s">
         <v>635</v>
@@ -27034,10 +27015,10 @@
         <v>145</v>
       </c>
       <c r="U365" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V365" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="366" spans="1:22">
@@ -27045,10 +27026,10 @@
         <v>72</v>
       </c>
       <c r="B366" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C366" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="D366" t="s">
         <v>123</v>
@@ -27072,7 +27053,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="K366" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L366" t="s">
         <v>635</v>
@@ -27093,10 +27074,10 @@
         <v>145</v>
       </c>
       <c r="U366" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V366" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="367" spans="1:22">
@@ -27104,10 +27085,10 @@
         <v>72</v>
       </c>
       <c r="B367" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="C367" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D367" t="s">
         <v>123</v>
@@ -27131,7 +27112,7 @@
         <v>0.5</v>
       </c>
       <c r="K367" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="L367" t="s">
         <v>86</v>
@@ -27146,16 +27127,16 @@
         <v>54</v>
       </c>
       <c r="S367" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="T367" t="s">
         <v>145</v>
       </c>
       <c r="U367" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V367" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
     </row>
     <row r="368" spans="1:22">
@@ -27163,10 +27144,10 @@
         <v>72</v>
       </c>
       <c r="B368" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="C368" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D368" t="s">
         <v>123</v>
@@ -27190,7 +27171,7 @@
         <v>0.5</v>
       </c>
       <c r="K368" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="L368" t="s">
         <v>86</v>
@@ -27205,16 +27186,16 @@
         <v>54</v>
       </c>
       <c r="S368" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="T368" t="s">
         <v>145</v>
       </c>
       <c r="U368" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V368" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
     </row>
     <row r="369" spans="1:22">
@@ -27222,10 +27203,10 @@
         <v>72</v>
       </c>
       <c r="B369" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C369" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D369" t="s">
         <v>123</v>
@@ -27249,7 +27230,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K369" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L369" t="s">
         <v>127</v>
@@ -27264,16 +27245,16 @@
         <v>54</v>
       </c>
       <c r="S369" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T369" t="s">
         <v>145</v>
       </c>
       <c r="U369" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V369" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="370" spans="1:22">
@@ -27281,10 +27262,10 @@
         <v>72</v>
       </c>
       <c r="B370" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C370" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D370" t="s">
         <v>123</v>
@@ -27308,7 +27289,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K370" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L370" t="s">
         <v>127</v>
@@ -27323,16 +27304,16 @@
         <v>54</v>
       </c>
       <c r="S370" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T370" t="s">
         <v>145</v>
       </c>
       <c r="U370" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V370" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="371" spans="1:22">
@@ -27340,10 +27321,10 @@
         <v>72</v>
       </c>
       <c r="B371" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C371" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D371" t="s">
         <v>123</v>
@@ -27367,7 +27348,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K371" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L371" t="s">
         <v>127</v>
@@ -27382,16 +27363,16 @@
         <v>54</v>
       </c>
       <c r="S371" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T371" t="s">
         <v>145</v>
       </c>
       <c r="U371" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V371" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="372" spans="1:22">
@@ -27399,10 +27380,10 @@
         <v>72</v>
       </c>
       <c r="B372" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C372" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D372" t="s">
         <v>123</v>
@@ -27426,7 +27407,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K372" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L372" t="s">
         <v>127</v>
@@ -27441,16 +27422,16 @@
         <v>54</v>
       </c>
       <c r="S372" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T372" t="s">
         <v>145</v>
       </c>
       <c r="U372" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V372" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="373" spans="1:22">
@@ -27458,10 +27439,10 @@
         <v>72</v>
       </c>
       <c r="B373" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C373" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D373" t="s">
         <v>123</v>
@@ -27485,7 +27466,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K373" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L373" t="s">
         <v>127</v>
@@ -27500,16 +27481,16 @@
         <v>54</v>
       </c>
       <c r="S373" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T373" t="s">
         <v>145</v>
       </c>
       <c r="U373" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V373" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="374" spans="1:22">
@@ -27517,10 +27498,10 @@
         <v>72</v>
       </c>
       <c r="B374" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C374" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D374" t="s">
         <v>123</v>
@@ -27544,7 +27525,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="K374" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L374" t="s">
         <v>127</v>
@@ -27559,16 +27540,16 @@
         <v>54</v>
       </c>
       <c r="S374" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="T374" t="s">
         <v>145</v>
       </c>
       <c r="U374" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V374" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="375" spans="1:22">
@@ -27576,10 +27557,10 @@
         <v>72</v>
       </c>
       <c r="B375" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C375" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="D375" t="s">
         <v>123</v>
@@ -27603,7 +27584,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K375" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L375" t="s">
         <v>127</v>
@@ -27624,10 +27605,10 @@
         <v>145</v>
       </c>
       <c r="U375" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V375" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
     </row>
     <row r="376" spans="1:22">
@@ -27635,10 +27616,10 @@
         <v>72</v>
       </c>
       <c r="B376" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C376" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D376" t="s">
         <v>123</v>
@@ -27662,7 +27643,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="K376" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L376" t="s">
         <v>127</v>
@@ -27677,16 +27658,16 @@
         <v>54</v>
       </c>
       <c r="S376" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="T376" t="s">
         <v>145</v>
       </c>
       <c r="U376" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V376" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="377" spans="1:22">
@@ -27694,10 +27675,10 @@
         <v>72</v>
       </c>
       <c r="B377" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C377" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="D377" t="s">
         <v>123</v>
@@ -27721,7 +27702,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K377" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L377" t="s">
         <v>127</v>
@@ -27739,10 +27720,10 @@
         <v>145</v>
       </c>
       <c r="U377" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V377" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
     </row>
     <row r="378" spans="1:22">
@@ -27750,10 +27731,10 @@
         <v>72</v>
       </c>
       <c r="B378" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C378" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D378" t="s">
         <v>123</v>
@@ -27777,7 +27758,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="K378" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="L378" t="s">
         <v>127</v>
@@ -27792,16 +27773,16 @@
         <v>54</v>
       </c>
       <c r="S378" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="T378" t="s">
         <v>145</v>
       </c>
       <c r="U378" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V378" s="14" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
     </row>
     <row r="379" spans="1:22">
@@ -27809,10 +27790,10 @@
         <v>72</v>
       </c>
       <c r="B379" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C379" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="D379" t="s">
         <v>123</v>
@@ -27836,10 +27817,10 @@
         <v>0.625</v>
       </c>
       <c r="K379" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="L379" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="M379" t="s">
         <v>78</v>
@@ -27851,16 +27832,16 @@
         <v>54</v>
       </c>
       <c r="S379" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="T379" t="s">
         <v>145</v>
       </c>
       <c r="U379" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V379" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="380" spans="1:22">
@@ -27868,10 +27849,10 @@
         <v>72</v>
       </c>
       <c r="B380" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C380" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="D380" t="s">
         <v>123</v>
@@ -27895,10 +27876,10 @@
         <v>0.75</v>
       </c>
       <c r="K380" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="L380" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="M380" t="s">
         <v>78</v>
@@ -27910,16 +27891,16 @@
         <v>54</v>
       </c>
       <c r="S380" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="T380" t="s">
         <v>145</v>
       </c>
       <c r="U380" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V380" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="381" spans="1:22">
@@ -27927,10 +27908,10 @@
         <v>72</v>
       </c>
       <c r="B381" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C381" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="D381" t="s">
         <v>123</v>
@@ -27954,10 +27935,10 @@
         <v>0.75</v>
       </c>
       <c r="K381" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="L381" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="M381" t="s">
         <v>78</v>
@@ -27969,16 +27950,16 @@
         <v>54</v>
       </c>
       <c r="S381" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="T381" t="s">
         <v>145</v>
       </c>
       <c r="U381" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V381" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="382" spans="1:22">
@@ -27986,10 +27967,10 @@
         <v>72</v>
       </c>
       <c r="B382" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C382" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="D382" t="s">
         <v>123</v>
@@ -28013,10 +27994,10 @@
         <v>0.75</v>
       </c>
       <c r="K382" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="L382" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="M382" t="s">
         <v>78</v>
@@ -28028,16 +28009,16 @@
         <v>54</v>
       </c>
       <c r="S382" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="T382" t="s">
         <v>145</v>
       </c>
       <c r="U382" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V382" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="383" spans="1:22">
@@ -28045,10 +28026,10 @@
         <v>72</v>
       </c>
       <c r="B383" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C383" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="D383" t="s">
         <v>123</v>
@@ -28072,10 +28053,10 @@
         <v>0.625</v>
       </c>
       <c r="K383" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="L383" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="M383" t="s">
         <v>78</v>
@@ -28087,16 +28068,16 @@
         <v>54</v>
       </c>
       <c r="S383" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="T383" t="s">
         <v>145</v>
       </c>
       <c r="U383" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V383" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="384" spans="1:22">
@@ -28104,10 +28085,10 @@
         <v>72</v>
       </c>
       <c r="B384" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C384" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D384" t="s">
         <v>123</v>
@@ -28131,10 +28112,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K384" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L384" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M384" t="s">
         <v>78</v>
@@ -28146,16 +28127,16 @@
         <v>54</v>
       </c>
       <c r="S384" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="T384" t="s">
         <v>145</v>
       </c>
       <c r="U384" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V384" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="385" spans="1:22">
@@ -28163,10 +28144,10 @@
         <v>72</v>
       </c>
       <c r="B385" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C385" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D385" t="s">
         <v>123</v>
@@ -28190,10 +28171,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K385" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L385" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M385" t="s">
         <v>78</v>
@@ -28205,16 +28186,16 @@
         <v>54</v>
       </c>
       <c r="S385" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="T385" t="s">
         <v>145</v>
       </c>
       <c r="U385" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V385" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="386" spans="1:22">
@@ -28222,10 +28203,10 @@
         <v>72</v>
       </c>
       <c r="B386" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C386" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D386" t="s">
         <v>123</v>
@@ -28249,10 +28230,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K386" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L386" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M386" t="s">
         <v>78</v>
@@ -28264,16 +28245,16 @@
         <v>54</v>
       </c>
       <c r="S386" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="T386" t="s">
         <v>145</v>
       </c>
       <c r="U386" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V386" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="387" spans="1:22">
@@ -28281,10 +28262,10 @@
         <v>72</v>
       </c>
       <c r="B387" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C387" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D387" t="s">
         <v>123</v>
@@ -28308,10 +28289,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K387" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L387" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M387" t="s">
         <v>78</v>
@@ -28326,10 +28307,10 @@
         <v>145</v>
       </c>
       <c r="U387" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V387" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="388" spans="1:22">
@@ -28337,10 +28318,10 @@
         <v>72</v>
       </c>
       <c r="B388" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C388" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D388" t="s">
         <v>123</v>
@@ -28364,10 +28345,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K388" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L388" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M388" t="s">
         <v>78</v>
@@ -28382,10 +28363,10 @@
         <v>145</v>
       </c>
       <c r="U388" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V388" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="389" spans="1:22">
@@ -28393,10 +28374,10 @@
         <v>72</v>
       </c>
       <c r="B389" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C389" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D389" t="s">
         <v>123</v>
@@ -28420,10 +28401,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="K389" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="L389" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="M389" t="s">
         <v>78</v>
@@ -28438,10 +28419,10 @@
         <v>145</v>
       </c>
       <c r="U389" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V389" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="390" spans="1:22">
@@ -28449,10 +28430,10 @@
         <v>72</v>
       </c>
       <c r="B390" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="C390" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="D390" t="s">
         <v>17</v>
@@ -28476,10 +28457,10 @@
         <v>0.625</v>
       </c>
       <c r="K390" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="L390" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="M390" t="s">
         <v>78</v>
@@ -28494,13 +28475,13 @@
         <v>267</v>
       </c>
       <c r="T390" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="U390" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V390" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="391" spans="1:22">
@@ -28508,10 +28489,10 @@
         <v>72</v>
       </c>
       <c r="B391" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="C391" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="D391" t="s">
         <v>123</v>
@@ -28535,10 +28516,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="K391" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="L391" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="M391" t="s">
         <v>78</v>
@@ -28550,10 +28531,10 @@
         <v>28</v>
       </c>
       <c r="U391" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V391" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="392" spans="1:22">
@@ -28564,7 +28545,7 @@
         <v>913</v>
       </c>
       <c r="C392" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="D392" t="s">
         <v>123</v>
@@ -28606,7 +28587,7 @@
         <v>145</v>
       </c>
       <c r="V392" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="393" spans="1:22">
@@ -28617,7 +28598,7 @@
         <v>913</v>
       </c>
       <c r="C393" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="D393" t="s">
         <v>123</v>
@@ -28659,7 +28640,7 @@
         <v>145</v>
       </c>
       <c r="V393" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="394" spans="1:22">
@@ -28667,10 +28648,10 @@
         <v>72</v>
       </c>
       <c r="B394" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="C394" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="D394" t="s">
         <v>123</v>
@@ -28694,7 +28675,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="K394" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="L394" t="s">
         <v>595</v>
@@ -28709,16 +28690,16 @@
         <v>54</v>
       </c>
       <c r="S394" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="T394" t="s">
         <v>145</v>
       </c>
       <c r="U394" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V394" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="395" spans="1:22">
@@ -28726,10 +28707,10 @@
         <v>72</v>
       </c>
       <c r="B395" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="C395" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="D395" t="s">
         <v>123</v>
@@ -28753,7 +28734,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="K395" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="L395" t="s">
         <v>595</v>
@@ -28768,16 +28749,16 @@
         <v>54</v>
       </c>
       <c r="S395" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="T395" t="s">
         <v>145</v>
       </c>
       <c r="U395" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="V395" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
